--- a/prop/translation/odm.xlsx
+++ b/prop/translation/odm.xlsx
@@ -50,7 +50,7 @@
     <t>1M+ Units Capacity</t>
   </si>
   <si>
-    <t>100万+ 年产能</t>
+    <t>100万+ 关节年产能</t>
   </si>
   <si>
     <t>Annual Production</t>
@@ -248,13 +248,13 @@
     <t>Define Task</t>
   </si>
   <si>
-    <t>需求锚定与任务解构</t>
+    <t>任务定义</t>
   </si>
   <si>
     <t>System requirement analysis and environmental parameter definition.</t>
   </si>
   <si>
-    <t>深度剖析系统需求，精确定义作业环境参数</t>
+    <t>深度分析系统需求，明确作业环境参数</t>
   </si>
   <si>
     <t>Step 02</t>
@@ -266,13 +266,13 @@
     <t>Confirm Spec</t>
   </si>
   <si>
-    <t>核心规格技术验证</t>
+    <t>规格确认</t>
   </si>
   <si>
     <t>Validation of kinematic constraints and payload specifications.</t>
   </si>
   <si>
-    <t>开展运动学约束模拟，确保负载规格的精准对齐</t>
+    <t>验证运动学约束，核准负载规格参数</t>
   </si>
   <si>
     <t>Step 03</t>
@@ -284,13 +284,13 @@
     <t>Hardware Config</t>
   </si>
   <si>
-    <t>定制硬件系统集成</t>
+    <t>硬件配置</t>
   </si>
   <si>
     <t>Mechanical assembly of custom actuators and sensory arrays.</t>
   </si>
   <si>
-    <t>实现定制化执行器与传感器阵列的高精度机械集成</t>
+    <t>实现定制执行器与传感器阵列的机械集成</t>
   </si>
   <si>
     <t>Step 04</t>
@@ -302,13 +302,13 @@
     <t>Software Stack</t>
   </si>
   <si>
-    <t>系统底座与算法部署</t>
+    <t>软件栈部署</t>
   </si>
   <si>
     <t>Deployment of real-time OS and neural control algorithms.</t>
   </si>
   <si>
-    <t>快速部署实时操作系统与先进神经控制算法</t>
+    <t>部署实时操作系统与控制算法</t>
   </si>
   <si>
     <t>Step 05</t>
@@ -320,13 +320,13 @@
     <t>Validation</t>
   </si>
   <si>
-    <t>仿真推演与安全审计</t>
+    <t>测试验证</t>
   </si>
   <si>
     <t>Stress testing and behavioral safety audit in sandbox simulation.</t>
   </si>
   <si>
-    <t>在沙盒仿真环境中开展全场景压力测试与行为安全审查</t>
+    <t>进行压力测试与行为安全审计</t>
   </si>
   <si>
     <t>Step 06</t>
@@ -338,13 +338,13 @@
     <t>Delivery</t>
   </si>
   <si>
-    <t>全球交付与生态接入</t>
+    <t>交付上线</t>
   </si>
   <si>
     <t>Global deployment and integration into existing infrastructure.</t>
   </si>
   <si>
-    <t>实现全球范围内的敏捷部署，无缝接入客户现有基础设施</t>
+    <t>实现全球化部署，并与现有基础设施无缝集成</t>
   </si>
 </sst>
 </file>
@@ -357,14 +357,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -820,148 +813,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1396,7 +1389,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" ht="67.5" spans="1:2">
+    <row r="10" ht="81" spans="1:2">
       <c r="A10" s="1" t="s">
         <v>18</v>
       </c>
